--- a/経営管理/02_財務・会計/売上利益管理/売上利益サマリー.xlsx
+++ b/経営管理/02_財務・会計/売上利益管理/売上利益サマリー.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -484,9 +484,9 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -592,7 +592,7 @@
       <c r="C5" s="4" t="n">
         <v>4508</v>
       </c>
-      <c r="D5" s="4" t="n"/>
+      <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="4" t="n">
         <v>4508</v>
       </c>
@@ -629,7 +629,7 @@
       <c r="C6" s="4" t="n">
         <v>390</v>
       </c>
-      <c r="D6" s="4" t="n"/>
+      <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="4" t="n">
         <v>390</v>
       </c>
@@ -666,7 +666,7 @@
       <c r="C7" s="4" t="n">
         <v>8302</v>
       </c>
-      <c r="D7" s="4" t="n"/>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="4" t="n">
         <v>8302</v>
       </c>
@@ -703,7 +703,7 @@
       <c r="C8" s="4" t="n">
         <v>9614</v>
       </c>
-      <c r="D8" s="4" t="n"/>
+      <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="4" t="n">
         <v>9614</v>
       </c>
@@ -740,7 +740,7 @@
       <c r="C9" s="4" t="n">
         <v>2819</v>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="4" t="n">
         <v>2819</v>
       </c>
@@ -855,7 +855,7 @@
       <c r="C12" s="4" t="n">
         <v>3372</v>
       </c>
-      <c r="D12" s="4" t="n"/>
+      <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="4" t="n">
         <v>3372</v>
       </c>
@@ -970,7 +970,7 @@
       <c r="C15" s="4" t="n">
         <v>5530</v>
       </c>
-      <c r="D15" s="4" t="n"/>
+      <c r="D15" s="3" t="inlineStr"/>
       <c r="E15" s="4" t="n">
         <v>5530</v>
       </c>
@@ -1124,7 +1124,7 @@
       <c r="C19" s="4" t="n">
         <v>4770</v>
       </c>
-      <c r="D19" s="4" t="n"/>
+      <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="4" t="n">
         <v>4770</v>
       </c>
@@ -1512,7 +1512,7 @@
       <c r="C29" s="4" t="n">
         <v>6310</v>
       </c>
-      <c r="D29" s="4" t="n"/>
+      <c r="D29" s="3" t="inlineStr"/>
       <c r="E29" s="4" t="n">
         <v>6310</v>
       </c>
@@ -1933,34 +1933,26 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>2026/03</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="n">
-        <v>7620</v>
-      </c>
-      <c r="D40" s="6" t="n">
-        <v>1880</v>
-      </c>
-      <c r="E40" s="6" t="n">
-        <v>9500</v>
-      </c>
-      <c r="F40" s="6" t="n">
-        <v>231475</v>
-      </c>
+          <t>2026/02</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr"/>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>+12.4%</t>
+          <t>利益計2994万/11件</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>大和田様・近江様・小池様・青木様</t>
+          <t>高橋様・杉浦様・辻元様・菊池様・中村様・後藤様</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>進行中</t>
+          <t>進行中(明細あり)</t>
         </is>
       </c>
     </row>
@@ -1972,34 +1964,135 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>7620</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>1880</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>9500</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>231475</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>+12.4%</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>大和田様・近江様・小池様・青木様</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
           <t>2026/04</t>
         </is>
       </c>
-      <c r="C41" s="6" t="n">
+      <c r="C42" s="6" t="n">
         <v>12530</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D42" s="6" t="n">
         <v>850</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E42" s="6" t="n">
         <v>13380</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F42" s="6" t="n">
         <v>244855</v>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>+40.8%</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>平松様・宮崎様・木間塚様・小泉様・吉名様・髙橋様</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>進行中</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr"/>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr"/>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>利益計3067万/12件</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>木間塚様・梅津様・佐藤（涼）・髙橋様①・髙橋様②・富地様</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>進行中(明細あり)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr"/>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>利益計3257万/11件</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>蛇嶋様・小池様・綱川様・渡辺様・佐藤拓・橋本様</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>進行中(明細あり)</t>
         </is>
       </c>
     </row>
@@ -2014,24 +2107,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:J124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>顧客別 売上・粗利 明細（第5期〜第6期）｜担当：石井</t>
+          <t>顧客別 売上・粗利・利益 明細（第5期〜第6期）｜利益は6期=PDF売上表より</t>
         </is>
       </c>
     </row>
@@ -2063,22 +2157,27 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>利益(万)</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>支社</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>銀行・売主</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>状況</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>タイプ</t>
         </is>
       </c>
     </row>
@@ -2104,24 +2203,25 @@
       <c r="E4" s="4" t="n">
         <v>2780</v>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2147,24 +2247,25 @@
       <c r="E5" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>エイト</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2190,24 +2291,25 @@
       <c r="E6" s="4" t="n">
         <v>450</v>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>武蔵野</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2233,24 +2335,25 @@
       <c r="E7" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>福岡</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>アジサイ</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2276,24 +2379,25 @@
       <c r="E8" s="4" t="n">
         <v>2500</v>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2319,24 +2423,25 @@
       <c r="E9" s="4" t="n">
         <v>930</v>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>福岡</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2362,24 +2467,25 @@
       <c r="E10" s="4" t="n">
         <v>2450</v>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2408,17 +2514,18 @@
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
           <t>建築請負</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2444,24 +2551,25 @@
       <c r="E12" s="4" t="n">
         <v>440</v>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>結城</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2487,24 +2595,25 @@
       <c r="E13" s="4" t="n">
         <v>650</v>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>投資</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2530,24 +2639,25 @@
       <c r="E14" s="4" t="n">
         <v>2700</v>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2573,24 +2683,25 @@
       <c r="E15" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr"/>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>愛知</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>エルスタット</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2616,24 +2727,25 @@
       <c r="E16" s="4" t="n">
         <v>170</v>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>愛知</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>投資</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2659,24 +2771,25 @@
       <c r="E17" s="4" t="n">
         <v>360</v>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>福岡</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>アジサイ</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2702,24 +2815,25 @@
       <c r="E18" s="4" t="n">
         <v>810</v>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2745,24 +2859,25 @@
       <c r="E19" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>現金</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2788,24 +2903,25 @@
       <c r="E20" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>愛知</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>東亞</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2834,17 +2950,18 @@
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
           <t>建設請負</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2870,24 +2987,25 @@
       <c r="E22" s="4" t="n">
         <v>640</v>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2913,24 +3031,25 @@
       <c r="E23" s="4" t="n">
         <v>764</v>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2956,24 +3075,25 @@
       <c r="E24" s="4" t="n">
         <v>710</v>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -2999,24 +3119,25 @@
       <c r="E25" s="4" t="n">
         <v>570</v>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>本承認</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3042,24 +3163,25 @@
       <c r="E26" s="4" t="n">
         <v>660</v>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>本承認</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3085,24 +3207,25 @@
       <c r="E27" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>FGH</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>本承認</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3128,24 +3251,25 @@
       <c r="E28" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>愛知</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>エイト</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>本承認</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3171,24 +3295,25 @@
       <c r="E29" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>福岡</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>アジサイ</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3214,24 +3339,25 @@
       <c r="E30" s="4" t="n">
         <v>2480</v>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>柴建</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3257,24 +3383,25 @@
       <c r="E31" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>仲介/リフォ</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3300,24 +3427,25 @@
       <c r="E32" s="4" t="n">
         <v>2300</v>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3343,24 +3471,25 @@
       <c r="E33" s="4" t="n">
         <v>1980</v>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3389,17 +3518,18 @@
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr"/>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
           <t>仕入開発</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3425,24 +3555,25 @@
       <c r="E35" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>仲介/リフォ</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3468,24 +3599,25 @@
       <c r="E36" s="4" t="n">
         <v>650</v>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>現金</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3511,24 +3643,25 @@
       <c r="E37" s="4" t="n">
         <v>303</v>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>反響建設</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3557,17 +3690,18 @@
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr"/>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
           <t>買取</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3594,15 +3728,16 @@
         <v>61</v>
       </c>
       <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr"/>
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3631,17 +3766,18 @@
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr"/>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
           <t>請負建設</t>
         </is>
       </c>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3667,24 +3803,25 @@
       <c r="E41" s="4" t="n">
         <v>685</v>
       </c>
-      <c r="F41" s="3" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3710,24 +3847,25 @@
       <c r="E42" s="4" t="n">
         <v>565</v>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>愛知</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>私募債切替</t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3753,24 +3891,25 @@
       <c r="E43" s="4" t="n">
         <v>585</v>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3796,24 +3935,25 @@
       <c r="E44" s="4" t="n">
         <v>510</v>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3839,24 +3979,25 @@
       <c r="E45" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>愛知</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>エイト</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3882,24 +4023,25 @@
       <c r="E46" s="4" t="n">
         <v>650</v>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3931,14 +4073,15 @@
           <t>自社</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -3964,24 +4107,25 @@
       <c r="E48" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr"/>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -4007,24 +4151,25 @@
       <c r="E49" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr"/>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -4050,24 +4195,25 @@
       <c r="E50" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="F50" s="3" t="inlineStr"/>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>FGH</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -4093,24 +4239,25 @@
       <c r="E51" s="4" t="n">
         <v>300</v>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr"/>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>FGH</t>
         </is>
       </c>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -4136,24 +4283,25 @@
       <c r="E52" s="4" t="n">
         <v>368</v>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="F52" s="3" t="inlineStr"/>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
         <is>
           <t>愛知</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>武蔵野</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -4182,17 +4330,18 @@
       <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
           <t>先付</t>
         </is>
       </c>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -4218,24 +4367,25 @@
       <c r="E54" s="4" t="n">
         <v>580</v>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F54" s="3" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -4261,24 +4411,25 @@
       <c r="E55" s="4" t="n">
         <v>680</v>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F55" s="3" t="inlineStr"/>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -4304,24 +4455,25 @@
       <c r="E56" s="4" t="n">
         <v>470</v>
       </c>
-      <c r="F56" s="3" t="inlineStr">
+      <c r="F56" s="3" t="inlineStr"/>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
         <is>
           <t>愛知</t>
         </is>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -4347,24 +4499,25 @@
       <c r="E57" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="F57" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr"/>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>現金</t>
         </is>
       </c>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -4390,24 +4543,25 @@
       <c r="E58" s="4" t="n">
         <v>600</v>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F58" s="3" t="inlineStr"/>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
         <is>
           <t>FGH</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -4433,24 +4587,25 @@
       <c r="E59" s="4" t="n">
         <v>550</v>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr"/>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>自社</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
         <is>
           <t>東京</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>自社</t>
         </is>
       </c>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>決済</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
         </is>
       </c>
     </row>
@@ -4470,26 +4625,21 @@
           <t>塚本様</t>
         </is>
       </c>
-      <c r="D60" s="4" t="n"/>
+      <c r="D60" s="3" t="inlineStr"/>
       <c r="E60" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="F60" s="3" t="inlineStr"/>
+      <c r="F60" s="4" t="n">
+        <v>323</v>
+      </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>投資</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>申込中</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>投資</t>
-        </is>
-      </c>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr"/>
+      <c r="I60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
@@ -4507,28 +4657,21 @@
           <t>井坂様</t>
         </is>
       </c>
-      <c r="D61" s="4" t="n">
-        <v>2500</v>
-      </c>
+      <c r="D61" s="3" t="inlineStr"/>
       <c r="E61" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F61" s="3" t="inlineStr"/>
+        <v>450</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>351</v>
+      </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t>申込中</t>
-        </is>
-      </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr"/>
+      <c r="J61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -4543,31 +4686,26 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>中村様</t>
+          <t>大崎様</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>2300</v>
+        <v>690</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="F62" s="3" t="inlineStr"/>
+        <v>690</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>645</v>
+      </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr">
-        <is>
-          <t>申込中</t>
-        </is>
-      </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr"/>
+      <c r="I62" s="3" t="inlineStr"/>
+      <c r="J62" s="3" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
@@ -4582,35 +4720,24 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>大崎様</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="n">
-        <v>2500</v>
-      </c>
+          <t>中村様</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr"/>
       <c r="E63" s="4" t="n">
-        <v>690</v>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
+        <v>500</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>390</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>本承認</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -4628,26 +4755,19 @@
           <t>冨地様</t>
         </is>
       </c>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n">
-        <v>300</v>
-      </c>
-      <c r="F64" s="3" t="inlineStr"/>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>エルスタッド様</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>申込中</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
@@ -4657,38 +4777,29 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2026/01</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>大和田様</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="3" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
+          <t>宇野様</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>190</v>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>決済</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -4698,38 +4809,29 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2026/01</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>近江様</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>2950</v>
-      </c>
-      <c r="E66" s="4" t="n"/>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
+          <t>市毛様</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>278</v>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>本審査中</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>私募債/その他</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
@@ -4739,38 +4841,29 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2026/01</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>小池様</t>
-        </is>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>700</v>
-      </c>
-      <c r="E67" s="4" t="n"/>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
+          <t>藤田様</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>95</v>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>決済</t>
-        </is>
-      </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>私募債/その他</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr"/>
+      <c r="J67" s="3" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -4780,38 +4873,29 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>2026/03</t>
+          <t>2026/01</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>青木様</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>1990</v>
-      </c>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
+          <t>佐藤様</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>95</v>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>本審査中</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>私募債/その他</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr"/>
+      <c r="I68" s="3" t="inlineStr"/>
+      <c r="J68" s="3" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
@@ -4821,38 +4905,29 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>2026/04</t>
+          <t>2026/02</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>平松様</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
+          <t>高橋様</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>351</v>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>事前承認・本審査</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr"/>
+      <c r="J69" s="3" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -4862,38 +4937,29 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>2026/04</t>
+          <t>2026/02</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>宮崎様</t>
-        </is>
-      </c>
-      <c r="D70" s="4" t="n">
-        <v>2890</v>
-      </c>
-      <c r="E70" s="4" t="n"/>
-      <c r="F70" s="3" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
+          <t>杉浦様</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>273</v>
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>事前承認・本審査</t>
-        </is>
-      </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr"/>
+      <c r="I70" s="3" t="inlineStr"/>
+      <c r="J70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
@@ -4903,38 +4969,29 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>2026/04</t>
+          <t>2026/02</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>木間塚様</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>2200</v>
-      </c>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="3" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
+          <t>辻元様</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="4" t="n">
+        <v>450</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>351</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr">
-        <is>
-          <t>事前承認・本審査</t>
-        </is>
-      </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr"/>
+      <c r="I71" s="3" t="inlineStr"/>
+      <c r="J71" s="3" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -4944,38 +5001,27 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>2026/04</t>
+          <t>2026/02</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>小泉様</t>
-        </is>
-      </c>
-      <c r="D72" s="4" t="n">
-        <v>1980</v>
-      </c>
-      <c r="E72" s="4" t="n"/>
-      <c r="F72" s="3" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
+          <t>菊池様</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="4" t="n">
+        <v>343</v>
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr">
-        <is>
-          <t>事前承認・本審査</t>
-        </is>
-      </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr"/>
+      <c r="I72" s="3" t="inlineStr"/>
+      <c r="J72" s="3" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
@@ -4985,38 +5031,29 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>2026/04</t>
+          <t>2026/02</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>吉名様</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>500</v>
-      </c>
-      <c r="E73" s="4" t="n"/>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
+          <t>中村様</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr"/>
+      <c r="E73" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>300</v>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr">
-        <is>
-          <t>事前審査準備</t>
-        </is>
-      </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+          <t>リフォーム</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr"/>
+      <c r="I73" s="3" t="inlineStr"/>
+      <c r="J73" s="3" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
@@ -5026,38 +5063,1643 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
+          <t>2026/02</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>後藤様</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="4" t="n">
+        <v>348</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>331</v>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="3" t="inlineStr"/>
+      <c r="J74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>2026/02</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>荒井様</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr"/>
+      <c r="J75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>2026/02</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>宇野様</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr"/>
+      <c r="E76" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="G76" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr"/>
+      <c r="J76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>2026/02</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>田中様</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>2026/02</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>橋本様</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr"/>
+      <c r="E78" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>2026/02</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>伊藤様</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr"/>
+      <c r="E79" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr"/>
+      <c r="J79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>大和田様</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr"/>
+      <c r="E80" s="4" t="n">
+        <v>590</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>近江様</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr"/>
+      <c r="E81" s="4" t="n">
+        <v>730</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>青木駿様</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr"/>
+      <c r="E82" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>343</v>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr"/>
+      <c r="J82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>小池様</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr"/>
+      <c r="E83" s="4" t="n">
+        <v>480</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>板敷様</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr"/>
+      <c r="E84" s="4" t="n">
+        <v>369</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>塚本様</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr"/>
+      <c r="E85" s="4" t="n">
+        <v>369</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>288</v>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr"/>
+      <c r="J85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>大崎様</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>リフォーム</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr"/>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>鳥潟様</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="G87" s="3" t="inlineStr">
+        <is>
+          <t>太陽光</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr"/>
+      <c r="J87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>北原様</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr"/>
+      <c r="E88" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr"/>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>山田様</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>390</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="G89" s="3" t="inlineStr">
+        <is>
+          <t>太陽光</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>2026/03</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>吉名様</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr"/>
+      <c r="J90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
           <t>2026/04</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>髙橋様</t>
-        </is>
-      </c>
-      <c r="D74" s="4" t="n">
-        <v>2980</v>
-      </c>
-      <c r="E74" s="4" t="n"/>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>東京</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>事前承認・本審査</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>自社</t>
-        </is>
-      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>宮崎様</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>650</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>540</v>
+      </c>
+      <c r="G91" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr"/>
+      <c r="J91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>平松様</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>600</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>490</v>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>小泉様</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>1980</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>530</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="G93" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr"/>
+      <c r="J93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>吉名様</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr"/>
+      <c r="I94" s="3" t="inlineStr"/>
+      <c r="J94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>菊池様</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr"/>
+      <c r="E95" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="G95" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr"/>
+      <c r="I95" s="3" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>大西様</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr"/>
+      <c r="E96" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr"/>
+      <c r="I96" s="3" t="inlineStr"/>
+      <c r="J96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>冨地様</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr"/>
+      <c r="E97" s="3" t="inlineStr"/>
+      <c r="F97" s="3" t="inlineStr"/>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr"/>
+      <c r="J97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>東亞様</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr"/>
+      <c r="E98" s="3" t="inlineStr"/>
+      <c r="F98" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr"/>
+      <c r="I98" s="3" t="inlineStr"/>
+      <c r="J98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>青木様</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>400</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>太陽光</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>杉浦様</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr"/>
+      <c r="E100" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>485</v>
+      </c>
+      <c r="G100" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr"/>
+      <c r="I100" s="3" t="inlineStr"/>
+      <c r="J100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>2026/04</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>小池様</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr"/>
+      <c r="E101" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>485</v>
+      </c>
+      <c r="G101" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr"/>
+      <c r="I101" s="3" t="inlineStr"/>
+      <c r="J101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>木間塚様</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr"/>
+      <c r="E102" s="4" t="n">
+        <v>550</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="G102" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr"/>
+      <c r="I102" s="3" t="inlineStr"/>
+      <c r="J102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>梅津様</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr"/>
+      <c r="E103" s="4" t="n">
+        <v>570</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>460</v>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="3" t="inlineStr"/>
+      <c r="J103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>佐藤（涼）</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr"/>
+      <c r="E104" s="4" t="n">
+        <v>475</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>371</v>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr"/>
+      <c r="J104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>髙橋様①</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr"/>
+      <c r="E105" s="4" t="n">
+        <v>620</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>510</v>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr"/>
+      <c r="J105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>髙橋様②</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr"/>
+      <c r="E106" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>297</v>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr"/>
+      <c r="I106" s="3" t="inlineStr"/>
+      <c r="J106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>富地様</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr"/>
+      <c r="E107" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr"/>
+      <c r="J107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>光田様</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr"/>
+      <c r="E108" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr"/>
+      <c r="I108" s="3" t="inlineStr"/>
+      <c r="J108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>小池様</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr"/>
+      <c r="E109" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr"/>
+      <c r="I109" s="3" t="inlineStr"/>
+      <c r="J109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>土田様</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr"/>
+      <c r="E110" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr"/>
+      <c r="I110" s="3" t="inlineStr"/>
+      <c r="J110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>秋吉様</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr"/>
+      <c r="E111" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>285</v>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr"/>
+      <c r="J111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>松倉様</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr"/>
+      <c r="E112" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="G112" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr"/>
+      <c r="I112" s="3" t="inlineStr"/>
+      <c r="J112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>2026/05</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>吉名様</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr"/>
+      <c r="E113" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>私募債</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr"/>
+      <c r="J113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>蛇嶋様</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr"/>
+      <c r="E114" s="4" t="n">
+        <v>490</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr"/>
+      <c r="I114" s="3" t="inlineStr"/>
+      <c r="J114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>小池様</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr"/>
+      <c r="E115" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>390</v>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr"/>
+      <c r="I115" s="3" t="inlineStr"/>
+      <c r="J115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>綱川様</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr"/>
+      <c r="E116" s="4" t="n">
+        <v>550</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="G116" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr"/>
+      <c r="I116" s="3" t="inlineStr"/>
+      <c r="J116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>渡辺様</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr"/>
+      <c r="E117" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>390</v>
+      </c>
+      <c r="G117" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr"/>
+      <c r="I117" s="3" t="inlineStr"/>
+      <c r="J117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>佐藤拓</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr"/>
+      <c r="E118" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>390</v>
+      </c>
+      <c r="G118" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr"/>
+      <c r="I118" s="3" t="inlineStr"/>
+      <c r="J118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>橋本様</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr"/>
+      <c r="E119" s="4" t="n">
+        <v>500</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>390</v>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr"/>
+      <c r="I119" s="3" t="inlineStr"/>
+      <c r="J119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>池田様</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr"/>
+      <c r="E120" s="4" t="n">
+        <v>550</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>440</v>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>不動産</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr"/>
+      <c r="I120" s="3" t="inlineStr"/>
+      <c r="J120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>宮崎様</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>164</v>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>リフォーム</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr"/>
+      <c r="J121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>木間塚様</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr"/>
+      <c r="E122" s="3" t="inlineStr"/>
+      <c r="F122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>蓄電池</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr"/>
+      <c r="I122" s="3" t="inlineStr"/>
+      <c r="J122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>佐藤涼</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>123</v>
+      </c>
+      <c r="G123" s="3" t="inlineStr">
+        <is>
+          <t>リフォーム</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr"/>
+      <c r="I123" s="3" t="inlineStr"/>
+      <c r="J123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>6期</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>2026/06</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>綱川様</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="G124" s="3" t="inlineStr">
+        <is>
+          <t>リフォーム</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr"/>
+      <c r="I124" s="3" t="inlineStr"/>
+      <c r="J124" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
